--- a/STACK_Policy_Master.xlsx
+++ b/STACK_Policy_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JayChittooran\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaychittooran/Downloads/STACK_Policy_Automation_GitHub_Package/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48A4C6C-91F8-42BD-A6B8-907C85D40F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC43DDC-748B-7A48-92EF-F34CA6323261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="8" r:id="rId1"/>
@@ -1676,13 +1676,13 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2117,14 +2117,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22.65" customHeight="1">
+    <row r="1" spans="1:8" ht="22.75" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -2156,7 +2156,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="16">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2174,7 +2174,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="16">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -2194,7 +2194,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" ht="16">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -2208,13 +2208,13 @@
       </c>
       <c r="E6" s="2">
         <f>COUNTIFS('State Scores'!G2:G51,"&gt;=60",'State Scores'!G2:G51,"&lt;80")</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="16">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -2234,7 +2234,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" ht="16">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -2248,13 +2248,13 @@
       </c>
       <c r="E8" s="2">
         <f>COUNTIF('State Scores'!G2:G51,"&lt;40")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" ht="16">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2269,13 +2269,13 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" ht="16">
       <c r="A10" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B10" s="2">
         <f>AVERAGE('State Scores'!G2:G51)</f>
-        <v>59.11</v>
+        <v>57.66</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2299,7 +2299,7 @@
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" ht="16">
       <c r="A12" s="2" t="s">
         <v>303</v>
       </c>
@@ -2314,7 +2314,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" ht="16">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2328,7 +2328,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" ht="42">
+    <row r="14" spans="1:8" ht="48">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -2342,7 +2342,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" ht="42">
+    <row r="15" spans="1:8" ht="48">
       <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
@@ -2356,7 +2356,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:8" ht="42">
+    <row r="16" spans="1:8" ht="48">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
@@ -2423,12 +2423,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M51"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="5" width="29" customWidth="1"/>
-    <col min="6" max="6" width="24.9140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="13" width="22" customWidth="1"/>
   </cols>
@@ -2474,7 +2474,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="56">
+    <row r="2" spans="1:13" ht="64">
       <c r="A2" s="9" t="s">
         <v>216</v>
       </c>
@@ -2482,20 +2482,20 @@
         <v>310</v>
       </c>
       <c r="C2" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D2" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" s="7">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G2" s="8">
         <f t="shared" ref="G2:G33" si="0">ROUND(20*(0.35*C2+0.15*D2+0.25*E2+0.25*F2),1)</f>
-        <v>72.5</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>54</v>
@@ -2516,7 +2516,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="70">
+    <row r="3" spans="1:13" ht="80">
       <c r="A3" s="9" t="s">
         <v>221</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="84">
+    <row r="4" spans="1:13" ht="96">
       <c r="A4" s="9" t="s">
         <v>93</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="70">
+    <row r="5" spans="1:13" ht="80">
       <c r="A5" s="9" t="s">
         <v>224</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="70">
+    <row r="6" spans="1:13" ht="80">
       <c r="A6" s="9" t="s">
         <v>83</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="70">
+    <row r="7" spans="1:13" ht="80">
       <c r="A7" s="9" t="s">
         <v>227</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="70">
+    <row r="8" spans="1:13" ht="80">
       <c r="A8" s="9" t="s">
         <v>229</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="56">
+    <row r="9" spans="1:13" ht="80">
       <c r="A9" s="9" t="s">
         <v>141</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="56">
+    <row r="10" spans="1:13" ht="64">
       <c r="A10" s="9" t="s">
         <v>232</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="56">
+    <row r="11" spans="1:13" ht="64">
       <c r="A11" s="9" t="s">
         <v>98</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="70">
+    <row r="12" spans="1:13" ht="80">
       <c r="A12" s="9" t="s">
         <v>235</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="70">
+    <row r="13" spans="1:13" ht="96">
       <c r="A13" s="9" t="s">
         <v>237</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="84">
+    <row r="14" spans="1:13" ht="96">
       <c r="A14" s="9" t="s">
         <v>103</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="84">
+    <row r="15" spans="1:13" ht="96">
       <c r="A15" s="9" t="s">
         <v>240</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="70">
+    <row r="16" spans="1:13" ht="80">
       <c r="A16" s="9" t="s">
         <v>242</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="56">
+    <row r="17" spans="1:13" ht="64">
       <c r="A17" s="9" t="s">
         <v>244</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="84">
+    <row r="18" spans="1:13" ht="96">
       <c r="A18" s="9" t="s">
         <v>153</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="84">
+    <row r="19" spans="1:13" ht="96">
       <c r="A19" s="9" t="s">
         <v>247</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="84">
+    <row r="20" spans="1:13" ht="96">
       <c r="A20" s="9" t="s">
         <v>249</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="84">
+    <row r="21" spans="1:13" ht="112">
       <c r="A21" s="9" t="s">
         <v>251</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="70">
+    <row r="22" spans="1:13" ht="96">
       <c r="A22" s="9" t="s">
         <v>253</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="84">
+    <row r="23" spans="1:13" ht="96">
       <c r="A23" s="9" t="s">
         <v>255</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="84">
+    <row r="24" spans="1:13" ht="96">
       <c r="A24" s="9" t="s">
         <v>257</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="70">
+    <row r="25" spans="1:13" ht="80">
       <c r="A25" s="9" t="s">
         <v>259</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="84">
+    <row r="26" spans="1:13" ht="96">
       <c r="A26" s="9" t="s">
         <v>261</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="70">
+    <row r="27" spans="1:13" ht="80">
       <c r="A27" s="9" t="s">
         <v>263</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="70">
+    <row r="28" spans="1:13" ht="80">
       <c r="A28" s="9" t="s">
         <v>166</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="70">
+    <row r="29" spans="1:13" ht="80">
       <c r="A29" s="9" t="s">
         <v>108</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="70">
+    <row r="30" spans="1:13" ht="80">
       <c r="A30" s="9" t="s">
         <v>267</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="84">
+    <row r="31" spans="1:13" ht="96">
       <c r="A31" s="9" t="s">
         <v>110</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="70">
+    <row r="32" spans="1:13" ht="80">
       <c r="A32" s="9" t="s">
         <v>180</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="84">
+    <row r="33" spans="1:13" ht="112">
       <c r="A33" s="9" t="s">
         <v>171</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="70">
+    <row r="34" spans="1:13" ht="96">
       <c r="A34" s="9" t="s">
         <v>272</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="8">
-        <f t="shared" ref="G34:G65" si="1">ROUND(20*(0.35*C34+0.15*D34+0.25*E34+0.25*F34),1)</f>
+        <f t="shared" ref="G34:G51" si="1">ROUND(20*(0.35*C34+0.15*D34+0.25*E34+0.25*F34),1)</f>
         <v>47.5</v>
       </c>
       <c r="H34" s="2" t="s">
@@ -3860,7 +3860,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="70">
+    <row r="35" spans="1:13" ht="80">
       <c r="A35" s="9" t="s">
         <v>274</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="70">
+    <row r="36" spans="1:13" ht="80">
       <c r="A36" s="9" t="s">
         <v>101</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="84">
+    <row r="37" spans="1:13" ht="96">
       <c r="A37" s="9" t="s">
         <v>277</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="70">
+    <row r="38" spans="1:13" ht="80">
       <c r="A38" s="9" t="s">
         <v>105</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="84">
+    <row r="39" spans="1:13" ht="96">
       <c r="A39" s="9" t="s">
         <v>147</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="84">
+    <row r="40" spans="1:13" ht="112">
       <c r="A40" s="9" t="s">
         <v>281</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="84">
+    <row r="41" spans="1:13" ht="96">
       <c r="A41" s="9" t="s">
         <v>283</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="70">
+    <row r="42" spans="1:13" ht="96">
       <c r="A42" s="9" t="s">
         <v>285</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="70">
+    <row r="43" spans="1:13" ht="96">
       <c r="A43" s="9" t="s">
         <v>287</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="84">
+    <row r="44" spans="1:13" ht="96">
       <c r="A44" s="9" t="s">
         <v>95</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="84">
+    <row r="45" spans="1:13" ht="96">
       <c r="A45" s="9" t="s">
         <v>290</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="84">
+    <row r="46" spans="1:13" ht="96">
       <c r="A46" s="9" t="s">
         <v>292</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="84">
+    <row r="47" spans="1:13" ht="96">
       <c r="A47" s="9" t="s">
         <v>90</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="70">
+    <row r="48" spans="1:13" ht="96">
       <c r="A48" s="9" t="s">
         <v>295</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="84">
+    <row r="49" spans="1:13" ht="112">
       <c r="A49" s="9" t="s">
         <v>297</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="84">
+    <row r="50" spans="1:13" ht="96">
       <c r="A50" s="9" t="s">
         <v>299</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="98">
+    <row r="51" spans="1:13" ht="112">
       <c r="A51" s="9" t="s">
         <v>189</v>
       </c>
@@ -4582,7 +4582,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P7"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -4744,7 +4744,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:V100"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -4827,7 +4827,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="56">
+    <row r="2" spans="1:22" ht="64">
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="V2" s="2"/>
     </row>
-    <row r="3" spans="1:22" ht="28">
+    <row r="3" spans="1:22" ht="32">
       <c r="A3" s="2" t="s">
         <v>90</v>
       </c>
@@ -4937,7 +4937,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="28">
+    <row r="4" spans="1:22" ht="32">
       <c r="A4" s="2" t="s">
         <v>93</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="28">
+    <row r="5" spans="1:22" ht="32">
       <c r="A5" s="2" t="s">
         <v>95</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="28">
+    <row r="6" spans="1:22" ht="32">
       <c r="A6" s="2" t="s">
         <v>95</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="28">
+    <row r="7" spans="1:22" ht="32">
       <c r="A7" s="2" t="s">
         <v>98</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="28">
+    <row r="8" spans="1:22" ht="32">
       <c r="A8" s="2" t="s">
         <v>98</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="28">
+    <row r="9" spans="1:22" ht="32">
       <c r="A9" s="2" t="s">
         <v>101</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="28">
+    <row r="10" spans="1:22" ht="32">
       <c r="A10" s="2" t="s">
         <v>103</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="28">
+    <row r="11" spans="1:22" ht="32">
       <c r="A11" s="2" t="s">
         <v>105</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="28">
+    <row r="12" spans="1:22" ht="32">
       <c r="A12" s="2" t="s">
         <v>83</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="28">
+    <row r="13" spans="1:22" ht="32">
       <c r="A13" s="2" t="s">
         <v>108</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="28">
+    <row r="14" spans="1:22" ht="32">
       <c r="A14" s="2" t="s">
         <v>110</v>
       </c>
@@ -5711,7 +5711,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:W14"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -5800,7 +5800,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="84">
+    <row r="2" spans="1:23" ht="96">
       <c r="A2" s="2" t="s">
         <v>131</v>
       </c>
@@ -5859,7 +5859,7 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
     </row>
-    <row r="3" spans="1:23" ht="112">
+    <row r="3" spans="1:23" ht="128">
       <c r="A3" s="2" t="s">
         <v>140</v>
       </c>
@@ -5918,7 +5918,7 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
     </row>
-    <row r="4" spans="1:23" ht="98">
+    <row r="4" spans="1:23" ht="112">
       <c r="A4" s="2" t="s">
         <v>146</v>
       </c>
@@ -5977,7 +5977,7 @@
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" spans="1:23" ht="84">
+    <row r="5" spans="1:23" ht="96">
       <c r="A5" s="2" t="s">
         <v>152</v>
       </c>
@@ -6036,7 +6036,7 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" spans="1:23" ht="98">
+    <row r="6" spans="1:23" ht="128">
       <c r="A6" s="2" t="s">
         <v>157</v>
       </c>
@@ -6095,7 +6095,7 @@
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
     </row>
-    <row r="7" spans="1:23" ht="84">
+    <row r="7" spans="1:23" ht="112">
       <c r="A7" s="2" t="s">
         <v>161</v>
       </c>
@@ -6154,7 +6154,7 @@
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
     </row>
-    <row r="8" spans="1:23" ht="70">
+    <row r="8" spans="1:23" ht="80">
       <c r="A8" s="2" t="s">
         <v>165</v>
       </c>
@@ -6213,7 +6213,7 @@
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
     </row>
-    <row r="9" spans="1:23" ht="84">
+    <row r="9" spans="1:23" ht="96">
       <c r="A9" s="2" t="s">
         <v>170</v>
       </c>
@@ -6272,7 +6272,7 @@
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
     </row>
-    <row r="10" spans="1:23" ht="70">
+    <row r="10" spans="1:23" ht="80">
       <c r="A10" s="2" t="s">
         <v>175</v>
       </c>
@@ -6331,7 +6331,7 @@
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
     </row>
-    <row r="11" spans="1:23" ht="84">
+    <row r="11" spans="1:23" ht="112">
       <c r="A11" s="2" t="s">
         <v>179</v>
       </c>
@@ -6390,7 +6390,7 @@
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
     </row>
-    <row r="12" spans="1:23" ht="84">
+    <row r="12" spans="1:23" ht="96">
       <c r="A12" s="2" t="s">
         <v>184</v>
       </c>
@@ -6449,7 +6449,7 @@
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
     </row>
-    <row r="13" spans="1:23" ht="84">
+    <row r="13" spans="1:23" ht="96">
       <c r="A13" s="2" t="s">
         <v>188</v>
       </c>
@@ -6508,7 +6508,7 @@
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
     </row>
-    <row r="14" spans="1:23" ht="84">
+    <row r="14" spans="1:23" ht="96">
       <c r="A14" s="2" t="s">
         <v>193</v>
       </c>
@@ -6584,7 +6584,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:P100"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="24" customWidth="1"/>
     <col min="9" max="16" width="22" customWidth="1"/>
@@ -6978,7 +6978,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:P51"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -7031,7 +7031,7 @@
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="28">
+    <row r="2" spans="1:16" ht="32">
       <c r="A2" s="2" t="s">
         <v>215</v>
       </c>
@@ -7064,7 +7064,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="28">
+    <row r="3" spans="1:16" ht="32">
       <c r="A3" s="2" t="s">
         <v>220</v>
       </c>
@@ -7097,7 +7097,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="28">
+    <row r="4" spans="1:16" ht="32">
       <c r="A4" s="2" t="s">
         <v>222</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="28">
+    <row r="5" spans="1:16" ht="32">
       <c r="A5" s="2" t="s">
         <v>223</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="28">
+    <row r="6" spans="1:16" ht="32">
       <c r="A6" s="2" t="s">
         <v>225</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="28">
+    <row r="7" spans="1:16" ht="32">
       <c r="A7" s="2" t="s">
         <v>226</v>
       </c>
@@ -7229,7 +7229,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="28">
+    <row r="8" spans="1:16" ht="32">
       <c r="A8" s="2" t="s">
         <v>228</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="28">
+    <row r="9" spans="1:16" ht="32">
       <c r="A9" s="2" t="s">
         <v>230</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="28">
+    <row r="10" spans="1:16" ht="32">
       <c r="A10" s="2" t="s">
         <v>231</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="28">
+    <row r="11" spans="1:16" ht="32">
       <c r="A11" s="2" t="s">
         <v>233</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="28">
+    <row r="12" spans="1:16" ht="32">
       <c r="A12" s="2" t="s">
         <v>234</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="28">
+    <row r="13" spans="1:16" ht="32">
       <c r="A13" s="2" t="s">
         <v>236</v>
       </c>
@@ -7427,7 +7427,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="28">
+    <row r="14" spans="1:16" ht="32">
       <c r="A14" s="2" t="s">
         <v>238</v>
       </c>
@@ -7460,7 +7460,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="28">
+    <row r="15" spans="1:16" ht="32">
       <c r="A15" s="2" t="s">
         <v>239</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="28">
+    <row r="16" spans="1:16" ht="32">
       <c r="A16" s="2" t="s">
         <v>241</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="28">
+    <row r="17" spans="1:13" ht="32">
       <c r="A17" s="2" t="s">
         <v>243</v>
       </c>
@@ -7559,7 +7559,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="28">
+    <row r="18" spans="1:13" ht="32">
       <c r="A18" s="2" t="s">
         <v>245</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="28">
+    <row r="19" spans="1:13" ht="32">
       <c r="A19" s="2" t="s">
         <v>246</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="28">
+    <row r="20" spans="1:13" ht="32">
       <c r="A20" s="2" t="s">
         <v>248</v>
       </c>
@@ -7658,7 +7658,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="28">
+    <row r="21" spans="1:13" ht="32">
       <c r="A21" s="2" t="s">
         <v>250</v>
       </c>
@@ -7691,7 +7691,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="28">
+    <row r="22" spans="1:13" ht="32">
       <c r="A22" s="2" t="s">
         <v>252</v>
       </c>
@@ -7724,7 +7724,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="28">
+    <row r="23" spans="1:13" ht="32">
       <c r="A23" s="2" t="s">
         <v>254</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="28">
+    <row r="24" spans="1:13" ht="32">
       <c r="A24" s="2" t="s">
         <v>256</v>
       </c>
@@ -7790,7 +7790,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="28">
+    <row r="25" spans="1:13" ht="32">
       <c r="A25" s="2" t="s">
         <v>258</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="28">
+    <row r="26" spans="1:13" ht="32">
       <c r="A26" s="2" t="s">
         <v>260</v>
       </c>
@@ -7856,7 +7856,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="28">
+    <row r="27" spans="1:13" ht="32">
       <c r="A27" s="2" t="s">
         <v>262</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="28">
+    <row r="28" spans="1:13" ht="32">
       <c r="A28" s="2" t="s">
         <v>264</v>
       </c>
@@ -7922,7 +7922,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="28">
+    <row r="29" spans="1:13" ht="32">
       <c r="A29" s="2" t="s">
         <v>265</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="28">
+    <row r="30" spans="1:13" ht="32">
       <c r="A30" s="2" t="s">
         <v>266</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="28">
+    <row r="31" spans="1:13" ht="32">
       <c r="A31" s="2" t="s">
         <v>268</v>
       </c>
@@ -8021,7 +8021,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="28">
+    <row r="32" spans="1:13" ht="32">
       <c r="A32" s="2" t="s">
         <v>269</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="28">
+    <row r="33" spans="1:13" ht="32">
       <c r="A33" s="2" t="s">
         <v>270</v>
       </c>
@@ -8087,7 +8087,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="28">
+    <row r="34" spans="1:13" ht="32">
       <c r="A34" s="2" t="s">
         <v>271</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28">
+    <row r="35" spans="1:13" ht="32">
       <c r="A35" s="2" t="s">
         <v>273</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="28">
+    <row r="36" spans="1:13" ht="32">
       <c r="A36" s="2" t="s">
         <v>275</v>
       </c>
@@ -8186,7 +8186,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="28">
+    <row r="37" spans="1:13" ht="32">
       <c r="A37" s="2" t="s">
         <v>276</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="28">
+    <row r="38" spans="1:13" ht="32">
       <c r="A38" s="2" t="s">
         <v>278</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="28">
+    <row r="39" spans="1:13" ht="32">
       <c r="A39" s="2" t="s">
         <v>279</v>
       </c>
@@ -8285,7 +8285,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="28">
+    <row r="40" spans="1:13" ht="32">
       <c r="A40" s="2" t="s">
         <v>280</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="28">
+    <row r="41" spans="1:13" ht="32">
       <c r="A41" s="2" t="s">
         <v>282</v>
       </c>
@@ -8351,7 +8351,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="28">
+    <row r="42" spans="1:13" ht="32">
       <c r="A42" s="2" t="s">
         <v>284</v>
       </c>
@@ -8384,7 +8384,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="28">
+    <row r="43" spans="1:13" ht="32">
       <c r="A43" s="2" t="s">
         <v>286</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="28">
+    <row r="44" spans="1:13" ht="32">
       <c r="A44" s="2" t="s">
         <v>288</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="28">
+    <row r="45" spans="1:13" ht="32">
       <c r="A45" s="2" t="s">
         <v>289</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="28">
+    <row r="46" spans="1:13" ht="32">
       <c r="A46" s="2" t="s">
         <v>291</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="28">
+    <row r="47" spans="1:13" ht="32">
       <c r="A47" s="2" t="s">
         <v>293</v>
       </c>
@@ -8549,7 +8549,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="28">
+    <row r="48" spans="1:13" ht="32">
       <c r="A48" s="2" t="s">
         <v>294</v>
       </c>
@@ -8582,7 +8582,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="28">
+    <row r="49" spans="1:13" ht="32">
       <c r="A49" s="2" t="s">
         <v>296</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="28">
+    <row r="50" spans="1:13" ht="32">
       <c r="A50" s="2" t="s">
         <v>298</v>
       </c>
@@ -8648,7 +8648,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="28">
+    <row r="51" spans="1:13" ht="32">
       <c r="A51" s="2" t="s">
         <v>300</v>
       </c>
@@ -8697,7 +8697,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
@@ -8728,7 +8728,7 @@
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" ht="16">
       <c r="A2" s="2" t="s">
         <v>403</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" ht="16">
       <c r="A3" s="2" t="s">
         <v>143</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" ht="16">
       <c r="A4" s="2" t="s">
         <v>405</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" ht="16">
       <c r="A5" s="2" t="s">
         <v>406</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" ht="16">
       <c r="A6" s="2" t="s">
         <v>407</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" ht="16">
       <c r="A7" s="2" t="s">
         <v>408</v>
       </c>
@@ -8776,7 +8776,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="28">
+    <row r="8" spans="1:16" ht="32">
       <c r="A8" s="2" t="s">
         <v>410</v>
       </c>
@@ -8784,7 +8784,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="42">
+    <row r="9" spans="1:16" ht="48">
       <c r="A9" s="2" t="s">
         <v>412</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="56">
+    <row r="10" spans="1:16" ht="64">
       <c r="A10" s="2" t="s">
         <v>414</v>
       </c>
@@ -8800,7 +8800,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="56">
+    <row r="11" spans="1:16" ht="64">
       <c r="A11" s="2" t="s">
         <v>405</v>
       </c>
@@ -8808,7 +8808,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="70">
+    <row r="12" spans="1:16" ht="80">
       <c r="A12" s="2" t="s">
         <v>417</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="70">
+    <row r="13" spans="1:16" ht="96">
       <c r="A13" s="2" t="s">
         <v>419</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="42">
+    <row r="14" spans="1:16" ht="48">
       <c r="A14" s="2" t="s">
         <v>421</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="28">
+    <row r="15" spans="1:16" ht="32">
       <c r="A15" s="2" t="s">
         <v>423</v>
       </c>
@@ -8840,7 +8840,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="28">
+    <row r="16" spans="1:16" ht="32">
       <c r="A16" s="2" t="s">
         <v>425</v>
       </c>
@@ -8856,7 +8856,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>

--- a/STACK_Policy_Master.xlsx
+++ b/STACK_Policy_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaychittooran/Downloads/STACK_Policy_Automation_GitHub_Package/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC43DDC-748B-7A48-92EF-F34CA6323261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575D2BF4-370E-5D4C-894B-2D7DCB37FD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B10" s="2">
         <f>AVERAGE('State Scores'!G2:G51)</f>
-        <v>57.66</v>
+        <v>58.06</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2482,20 +2482,20 @@
         <v>310</v>
       </c>
       <c r="C2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="8">
         <f t="shared" ref="G2:G33" si="0">ROUND(20*(0.35*C2+0.15*D2+0.25*E2+0.25*F2),1)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>54</v>

--- a/STACK_Policy_Master.xlsx
+++ b/STACK_Policy_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaychittooran/Downloads/STACK_Policy_Automation_GitHub_Package/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575D2BF4-370E-5D4C-894B-2D7DCB37FD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4633E724-7C17-8648-A6C0-3070EDB48F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1676,13 +1676,13 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E6" s="2">
         <f>COUNTIFS('State Scores'!G2:G51,"&gt;=60",'State Scores'!G2:G51,"&lt;80")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E8" s="2">
         <f>COUNTIF('State Scores'!G2:G51,"&lt;40")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B10" s="2">
         <f>AVERAGE('State Scores'!G2:G51)</f>
-        <v>58.06</v>
+        <v>59.11</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2482,20 +2482,20 @@
         <v>310</v>
       </c>
       <c r="C2" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2" s="7">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G2" s="8">
         <f t="shared" ref="G2:G33" si="0">ROUND(20*(0.35*C2+0.15*D2+0.25*E2+0.25*F2),1)</f>
-        <v>20</v>
+        <v>72.5</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>54</v>

--- a/STACK_Policy_Master.xlsx
+++ b/STACK_Policy_Master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaychittooran/Downloads/STACK_Policy_Automation_GitHub_Package/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaychittooran/Documents/STACK Policy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4633E724-7C17-8648-A6C0-3070EDB48F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6895A3F-E226-3C4D-9359-15DFBFD4D186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1676,13 +1676,13 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E6" s="2">
         <f>COUNTIFS('State Scores'!G2:G51,"&gt;=60",'State Scores'!G2:G51,"&lt;80")</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E8" s="2">
         <f>COUNTIF('State Scores'!G2:G51,"&lt;40")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B10" s="2">
         <f>AVERAGE('State Scores'!G2:G51)</f>
-        <v>59.11</v>
+        <v>58.06</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2482,20 +2482,20 @@
         <v>310</v>
       </c>
       <c r="C2" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2" s="7">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="G2" s="8">
         <f t="shared" ref="G2:G33" si="0">ROUND(20*(0.35*C2+0.15*D2+0.25*E2+0.25*F2),1)</f>
-        <v>72.5</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>54</v>
